--- a/src/app/modules/dashboard/excel_files/whole-food-plant-based-burgers-gyros-and-subs.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-food-plant-based-burgers-gyros-and-subs.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9723,7 +9723,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -11653,7 +11653,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -11845,7 +11845,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -13585,7 +13585,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -14151,7 +14151,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'burgers', 'wraps', 'sandwiches', 'gyro']</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
